--- a/artfynd/A 16316-2025 artfynd.xlsx
+++ b/artfynd/A 16316-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80914369</v>
+        <v>80914138</v>
       </c>
       <c r="B2" t="n">
-        <v>96245</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223572</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,14 +710,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>avk2019MITT563, Jmt</t>
+          <t>avk2019MITT376, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548151.0737172529</v>
+        <v>548162</v>
       </c>
       <c r="R2" t="n">
-        <v>7035194.903714888</v>
+        <v>7035201</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -739,7 +734,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Ångermanland</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -753,19 +748,9 @@
           <t>2019-06-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-06-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -794,6 +779,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>80914369</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99028</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>223572</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blodnycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. cruenta</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(O F.Müll.) Hyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>avk2019MITT563, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>548151</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7035195</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-06-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-06-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Klas Andersson, Magnus Sjölund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 16316-2025 artfynd.xlsx
+++ b/artfynd/A 16316-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80914138</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80914369</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>